--- a/Короткие названия.xlsx
+++ b/Короткие названия.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rogovi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACBFA35-E4EB-4C7F-A020-7694982B3309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CB6506-7475-4D41-844E-91223347B221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C75C0F7F-FE97-4E9D-8E7A-FB1708BCE888}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>Оригинальное название</t>
   </si>
@@ -45,41 +45,473 @@
     <t>Короткое название</t>
   </si>
   <si>
-    <t>Обсессия, Закулисье реальности, Мортал Комбат 2, Бухта вдов, Reanimal / Душевный подкаст 167</t>
-  </si>
-  <si>
-    <t>007 First Light, «Паук-Нуар», Summer Game Fest, Kane &amp; Lynch 2 / Душевный подкаст 166</t>
-  </si>
-  <si>
-    <t>«Пацаны: сезон 5», Mixtape, HoMM: Olden Era, «Каратель: Последнее убийство» / Душевный подкаст 165</t>
-  </si>
-  <si>
-    <t>Saros, Replaced, Pragmata, «Частный детектив МАУС», «Клиника» / Душевный подкаст 164</t>
-  </si>
-  <si>
-    <t>«Питт: Сезон 2», «Аватар: Пламя и пепел», Samson, «Молодой Шерлок» / Душевный подкаст 163</t>
-  </si>
-  <si>
-    <t>Выпуск 167</t>
-  </si>
-  <si>
-    <t>Выпуск 166</t>
-  </si>
-  <si>
-    <t>Выпуск 165</t>
-  </si>
-  <si>
-    <t>Выпуск 164</t>
-  </si>
-  <si>
-    <t>Выпуск 163</t>
+    <t>Выпуск 1</t>
+  </si>
+  <si>
+    <t>Выпуск 2</t>
+  </si>
+  <si>
+    <t>Выпуск 3</t>
+  </si>
+  <si>
+    <t>Выпуск 5</t>
+  </si>
+  <si>
+    <t>Выпуск 6</t>
+  </si>
+  <si>
+    <t>Выпуск 7</t>
+  </si>
+  <si>
+    <t>Выпуск 8</t>
+  </si>
+  <si>
+    <t>Выпуск 9</t>
+  </si>
+  <si>
+    <t>Выпуск 10</t>
+  </si>
+  <si>
+    <t>Выпуск 11</t>
+  </si>
+  <si>
+    <t>Выпуск 12</t>
+  </si>
+  <si>
+    <t>Выпуск 13</t>
+  </si>
+  <si>
+    <t>Выпуск 14</t>
+  </si>
+  <si>
+    <t>Выпуск 15</t>
+  </si>
+  <si>
+    <t>Выпуск 16</t>
+  </si>
+  <si>
+    <t>Выпуск 17</t>
+  </si>
+  <si>
+    <t>Выпуск 18</t>
+  </si>
+  <si>
+    <t>Выпуск 19</t>
+  </si>
+  <si>
+    <t>Выпуск 20</t>
+  </si>
+  <si>
+    <t>Выпуск 21</t>
+  </si>
+  <si>
+    <t>Выпуск 22</t>
+  </si>
+  <si>
+    <t>Выпуск 23</t>
+  </si>
+  <si>
+    <t>Выпуск 24</t>
+  </si>
+  <si>
+    <t>Выпуск 25</t>
+  </si>
+  <si>
+    <t>Выпуск 26</t>
+  </si>
+  <si>
+    <t>Выпуск 27</t>
+  </si>
+  <si>
+    <t>Выпуск 28</t>
+  </si>
+  <si>
+    <t>Выпуск 29</t>
+  </si>
+  <si>
+    <t>Выпуск 30</t>
+  </si>
+  <si>
+    <t>Выпуск 31</t>
+  </si>
+  <si>
+    <t>Выпуск 32</t>
+  </si>
+  <si>
+    <t>Выпуск 33</t>
+  </si>
+  <si>
+    <t>Выпуск 34</t>
+  </si>
+  <si>
+    <t>Выпуск 35</t>
+  </si>
+  <si>
+    <t>Выпуск 36</t>
+  </si>
+  <si>
+    <t>Выпуск 37</t>
+  </si>
+  <si>
+    <t>Выпуск 38</t>
+  </si>
+  <si>
+    <t>Выпуск 39</t>
+  </si>
+  <si>
+    <t>Выпуск 40</t>
+  </si>
+  <si>
+    <t>Выпуск 41</t>
+  </si>
+  <si>
+    <t>Выпуск 42</t>
+  </si>
+  <si>
+    <t>Выпуск 43</t>
+  </si>
+  <si>
+    <t>Выпуск 44</t>
+  </si>
+  <si>
+    <t>Выпуск 45</t>
+  </si>
+  <si>
+    <t>Выпуск 46</t>
+  </si>
+  <si>
+    <t>Выпуск 47</t>
+  </si>
+  <si>
+    <t>Выпуск 48</t>
+  </si>
+  <si>
+    <t>Выпуск 49</t>
+  </si>
+  <si>
+    <t>Выпуск 50</t>
+  </si>
+  <si>
+    <t>Выпуск 51</t>
+  </si>
+  <si>
+    <t>Выпуск 52</t>
+  </si>
+  <si>
+    <t>Выпуск 53</t>
+  </si>
+  <si>
+    <t>Выпуск 54</t>
+  </si>
+  <si>
+    <t>Выпуск 55</t>
+  </si>
+  <si>
+    <t>Выпуск 56</t>
+  </si>
+  <si>
+    <t>Выпуск 57</t>
+  </si>
+  <si>
+    <t>Выпуск 58</t>
+  </si>
+  <si>
+    <t>Выпуск 59</t>
+  </si>
+  <si>
+    <t>Выпуск 60</t>
+  </si>
+  <si>
+    <t>Выпуск 61</t>
+  </si>
+  <si>
+    <t>Выпуск 62</t>
+  </si>
+  <si>
+    <t>Выпуск 63</t>
+  </si>
+  <si>
+    <t>Выпуск 64</t>
+  </si>
+  <si>
+    <t>Выпуск 65</t>
+  </si>
+  <si>
+    <t>Выпуск 66</t>
+  </si>
+  <si>
+    <t>Выпуск 67</t>
+  </si>
+  <si>
+    <t>Выпуск 68</t>
+  </si>
+  <si>
+    <t>Выпуск 69</t>
+  </si>
+  <si>
+    <t>Выпуск 70</t>
+  </si>
+  <si>
+    <t>Выпуск 71</t>
+  </si>
+  <si>
+    <t>Выпуск 72</t>
+  </si>
+  <si>
+    <t>Выпуск 73</t>
+  </si>
+  <si>
+    <t>Выпуск 74</t>
+  </si>
+  <si>
+    <t>Выпуск 75</t>
+  </si>
+  <si>
+    <t>Выпуск 76</t>
+  </si>
+  <si>
+    <t>Выпуск 77</t>
+  </si>
+  <si>
+    <t>Выпуск 78</t>
+  </si>
+  <si>
+    <t>Выпуск 79</t>
+  </si>
+  <si>
+    <t>Выпуск 80</t>
+  </si>
+  <si>
+    <t>Выпуск 81</t>
+  </si>
+  <si>
+    <t>Выпуск 82</t>
+  </si>
+  <si>
+    <t>Выпуск 83</t>
+  </si>
+  <si>
+    <t>Выпуск 84</t>
+  </si>
+  <si>
+    <t>Выпуск 85</t>
+  </si>
+  <si>
+    <t>Выпуск 86</t>
+  </si>
+  <si>
+    <t>Выпуск 87</t>
+  </si>
+  <si>
+    <t>Выпуск 88</t>
+  </si>
+  <si>
+    <t>Выпуск 89</t>
+  </si>
+  <si>
+    <t>Выпуск 90</t>
+  </si>
+  <si>
+    <t>Выпуск 91</t>
+  </si>
+  <si>
+    <t>Выпуск 92</t>
+  </si>
+  <si>
+    <t>Выпуск 93</t>
+  </si>
+  <si>
+    <t>Выпуск 94</t>
+  </si>
+  <si>
+    <t>Выпуск 95</t>
+  </si>
+  <si>
+    <t>Выпуск 96</t>
+  </si>
+  <si>
+    <t>Выпуск 97</t>
+  </si>
+  <si>
+    <t>Выпуск 98</t>
+  </si>
+  <si>
+    <t>Выпуск 99</t>
+  </si>
+  <si>
+    <t>Выпуск 100</t>
+  </si>
+  <si>
+    <t>Выпуск 101</t>
+  </si>
+  <si>
+    <t>Выпуск 102</t>
+  </si>
+  <si>
+    <t>Выпуск 103</t>
+  </si>
+  <si>
+    <t>Выпуск 104</t>
+  </si>
+  <si>
+    <t>Выпуск 105</t>
+  </si>
+  <si>
+    <t>Выпуск 106</t>
+  </si>
+  <si>
+    <t>Выпуск 107</t>
+  </si>
+  <si>
+    <t>Выпуск 108</t>
+  </si>
+  <si>
+    <t>Выпуск 109</t>
+  </si>
+  <si>
+    <t>Выпуск 110</t>
+  </si>
+  <si>
+    <t>Выпуск 111</t>
+  </si>
+  <si>
+    <t>Выпуск 112</t>
+  </si>
+  <si>
+    <t>Выпуск 113</t>
+  </si>
+  <si>
+    <t>Выпуск 114</t>
+  </si>
+  <si>
+    <t>Выпуск 115</t>
+  </si>
+  <si>
+    <t>Выпуск 116</t>
+  </si>
+  <si>
+    <t>Выпуск 117</t>
+  </si>
+  <si>
+    <t>Выпуск 118</t>
+  </si>
+  <si>
+    <t>Выпуск 119</t>
+  </si>
+  <si>
+    <t>Выпуск 120</t>
+  </si>
+  <si>
+    <t>Выпуск 121</t>
+  </si>
+  <si>
+    <t>Выпуск 122</t>
+  </si>
+  <si>
+    <t>Выпуск 123</t>
+  </si>
+  <si>
+    <t>Выпуск 124</t>
+  </si>
+  <si>
+    <t>Выпуск 125</t>
+  </si>
+  <si>
+    <t>Выпуск 126</t>
+  </si>
+  <si>
+    <t>Выпуск 127</t>
+  </si>
+  <si>
+    <t>Выпуск 128</t>
+  </si>
+  <si>
+    <t>Выпуск 129</t>
+  </si>
+  <si>
+    <t>Выпуск 130</t>
+  </si>
+  <si>
+    <t>Выпуск 131</t>
+  </si>
+  <si>
+    <t>Выпуск 132</t>
+  </si>
+  <si>
+    <t>Выпуск 133</t>
+  </si>
+  <si>
+    <t>Выпуск 134</t>
+  </si>
+  <si>
+    <t>Выпуск 135</t>
+  </si>
+  <si>
+    <t>Выпуск 136</t>
+  </si>
+  <si>
+    <t>Выпуск 137</t>
+  </si>
+  <si>
+    <t>Выпуск 138</t>
+  </si>
+  <si>
+    <t>Выпуск 139</t>
+  </si>
+  <si>
+    <t>Выпуск 140</t>
+  </si>
+  <si>
+    <t>Выпуск 141</t>
+  </si>
+  <si>
+    <t>Выпуск 142</t>
+  </si>
+  <si>
+    <t>Выпуск 143</t>
+  </si>
+  <si>
+    <t>Выпуск 144</t>
+  </si>
+  <si>
+    <t>Выпуск 145</t>
+  </si>
+  <si>
+    <t>Выпуск 146</t>
+  </si>
+  <si>
+    <t>Выпуск 147</t>
+  </si>
+  <si>
+    <t>Выпуск 148</t>
+  </si>
+  <si>
+    <t>Выпуск 149</t>
+  </si>
+  <si>
+    <t>Выпуск 150</t>
+  </si>
+  <si>
+    <t>Выпуск 151</t>
+  </si>
+  <si>
+    <t>Выпуск 152</t>
+  </si>
+  <si>
+    <t>Выпуск 153</t>
+  </si>
+  <si>
+    <t>Выпуск 154</t>
+  </si>
+  <si>
+    <t>Выпуск 155</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,13 +533,6 @@
       <name val="Segoe UI"/>
       <family val="2"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -478,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7C6AF9-5F0C-4EB9-8185-62F3B09665F4}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="49.375" customWidth="1"/>
@@ -493,48 +918,1393 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="16.5">
+      <c r="A2" s="2" t="str">
+        <f>B2</f>
+        <v>Выпуск 1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="16.5">
+      <c r="A3" s="2" t="str">
+        <f t="shared" ref="A3:A66" si="0">B3</f>
+        <v>Выпуск 2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.5">
+      <c r="A4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16.5">
+      <c r="A5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 155</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.5">
+      <c r="A6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.5">
+      <c r="A7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.5">
+      <c r="A8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="9" spans="1:2" ht="16.5">
+      <c r="A9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 8</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="49.5">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="10" spans="1:2" ht="16.5">
+      <c r="A10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="33">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="11" spans="1:2" ht="16.5">
+      <c r="A11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 10</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="33">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="12" spans="1:2" ht="16.5">
+      <c r="A12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 11</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="13" spans="1:2" ht="16.5">
+      <c r="A13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16.5">
+      <c r="A14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16.5">
+      <c r="A15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16.5">
+      <c r="A16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16.5">
+      <c r="A17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16.5">
+      <c r="A18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="16.5">
+      <c r="A19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16.5">
+      <c r="A20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="16.5">
+      <c r="A21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="16.5">
+      <c r="A22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16.5">
+      <c r="A23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="16.5">
+      <c r="A24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16.5">
+      <c r="A25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="16.5">
+      <c r="A26" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="16.5">
+      <c r="A27" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="16.5">
+      <c r="A28" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="16.5">
+      <c r="A29" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="16.5">
+      <c r="A30" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="16.5">
+      <c r="A31" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="16.5">
+      <c r="A32" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="16.5">
+      <c r="A33" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="16.5">
+      <c r="A34" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="16.5">
+      <c r="A35" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="16.5">
+      <c r="A36" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="16.5">
+      <c r="A37" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="16.5">
+      <c r="A38" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="16.5">
+      <c r="A39" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="16.5">
+      <c r="A40" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="16.5">
+      <c r="A41" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="16.5">
+      <c r="A42" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="16.5">
+      <c r="A43" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="16.5">
+      <c r="A44" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="16.5">
+      <c r="A45" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="16.5">
+      <c r="A46" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="16.5">
+      <c r="A47" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="16.5">
+      <c r="A48" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="16.5">
+      <c r="A49" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="16.5">
+      <c r="A50" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="16.5">
+      <c r="A51" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="16.5">
+      <c r="A52" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="16.5">
+      <c r="A53" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="16.5">
+      <c r="A54" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="16.5">
+      <c r="A55" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="16.5">
+      <c r="A56" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="16.5">
+      <c r="A57" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="16.5">
+      <c r="A58" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="16.5">
+      <c r="A59" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="16.5">
+      <c r="A60" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="16.5">
+      <c r="A61" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="16.5">
+      <c r="A62" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="16.5">
+      <c r="A63" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 62</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="16.5">
+      <c r="A64" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 63</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="16.5">
+      <c r="A65" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 64</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="16.5">
+      <c r="A66" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Выпуск 65</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="16.5">
+      <c r="A67" s="2" t="str">
+        <f t="shared" ref="A67:A130" si="1">B67</f>
+        <v>Выпуск 66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="16.5">
+      <c r="A68" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 67</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="16.5">
+      <c r="A69" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 68</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="16.5">
+      <c r="A70" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 69</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="16.5">
+      <c r="A71" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="16.5">
+      <c r="A72" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 71</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="16.5">
+      <c r="A73" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 72</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="16.5">
+      <c r="A74" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 73</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="16.5">
+      <c r="A75" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 74</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="16.5">
+      <c r="A76" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="16.5">
+      <c r="A77" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="16.5">
+      <c r="A78" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="16.5">
+      <c r="A79" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="16.5">
+      <c r="A80" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="16.5">
+      <c r="A81" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="16.5">
+      <c r="A82" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 81</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="16.5">
+      <c r="A83" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="16.5">
+      <c r="A84" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 83</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="16.5">
+      <c r="A85" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="16.5">
+      <c r="A86" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="16.5">
+      <c r="A87" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="16.5">
+      <c r="A88" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="16.5">
+      <c r="A89" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="16.5">
+      <c r="A90" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="16.5">
+      <c r="A91" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="16.5">
+      <c r="A92" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="16.5">
+      <c r="A93" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="16.5">
+      <c r="A94" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="16.5">
+      <c r="A95" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="16.5">
+      <c r="A96" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 95</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="16.5">
+      <c r="A97" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 96</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="16.5">
+      <c r="A98" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 97</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="16.5">
+      <c r="A99" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 98</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="16.5">
+      <c r="A100" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="16.5">
+      <c r="A101" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 100</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="16.5">
+      <c r="A102" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 101</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="16.5">
+      <c r="A103" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 102</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="16.5">
+      <c r="A104" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 103</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="16.5">
+      <c r="A105" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 104</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="16.5">
+      <c r="A106" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 105</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="16.5">
+      <c r="A107" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 106</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="16.5">
+      <c r="A108" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 107</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="16.5">
+      <c r="A109" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 108</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="16.5">
+      <c r="A110" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="16.5">
+      <c r="A111" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="16.5">
+      <c r="A112" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 111</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="16.5">
+      <c r="A113" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="16.5">
+      <c r="A114" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 113</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="16.5">
+      <c r="A115" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 114</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="16.5">
+      <c r="A116" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 115</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="16.5">
+      <c r="A117" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 116</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="16.5">
+      <c r="A118" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 117</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="16.5">
+      <c r="A119" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 118</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="16.5">
+      <c r="A120" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 119</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="16.5">
+      <c r="A121" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 120</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="16.5">
+      <c r="A122" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 121</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="16.5">
+      <c r="A123" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 122</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="16.5">
+      <c r="A124" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 123</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="16.5">
+      <c r="A125" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 124</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="16.5">
+      <c r="A126" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 125</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="16.5">
+      <c r="A127" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 126</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="16.5">
+      <c r="A128" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 127</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="16.5">
+      <c r="A129" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 128</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="16.5">
+      <c r="A130" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Выпуск 129</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="16.5">
+      <c r="A131" s="2" t="str">
+        <f t="shared" ref="A131:A155" si="2">B131</f>
+        <v>Выпуск 130</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="16.5">
+      <c r="A132" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 131</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="16.5">
+      <c r="A133" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 132</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="16.5">
+      <c r="A134" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 133</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="16.5">
+      <c r="A135" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 134</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="16.5">
+      <c r="A136" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 135</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="16.5">
+      <c r="A137" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 136</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="16.5">
+      <c r="A138" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 137</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="16.5">
+      <c r="A139" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 138</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="16.5">
+      <c r="A140" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 139</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="16.5">
+      <c r="A141" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 140</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="16.5">
+      <c r="A142" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 141</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="16.5">
+      <c r="A143" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 142</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="16.5">
+      <c r="A144" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 143</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="16.5">
+      <c r="A145" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 144</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="16.5">
+      <c r="A146" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 145</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="16.5">
+      <c r="A147" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 146</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="16.5">
+      <c r="A148" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 147</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="16.5">
+      <c r="A149" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 148</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="16.5">
+      <c r="A150" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 149</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="16.5">
+      <c r="A151" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 150</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="16.5">
+      <c r="A152" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 151</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="16.5">
+      <c r="A153" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 152</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="16.5">
+      <c r="A154" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 153</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="16.5">
+      <c r="A155" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Выпуск 154</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Короткие названия.xlsx
+++ b/Короткие названия.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rogovi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\98rog\Desktop\Скуфим о Главном\Модель\Дашборд\Демо\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CB6506-7475-4D41-844E-91223347B221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07A7983-8A46-459A-B1B0-CA160B192501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C75C0F7F-FE97-4E9D-8E7A-FB1708BCE888}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{C75C0F7F-FE97-4E9D-8E7A-FB1708BCE888}"/>
   </bookViews>
   <sheets>
     <sheet name="Короткие названия" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="156">
   <si>
     <t>Оригинальное название</t>
   </si>
@@ -45,15 +47,15 @@
     <t>Короткое название</t>
   </si>
   <si>
+    <t>Выпуск 3</t>
+  </si>
+  <si>
     <t>Выпуск 1</t>
   </si>
   <si>
     <t>Выпуск 2</t>
   </si>
   <si>
-    <t>Выпуск 3</t>
-  </si>
-  <si>
     <t>Выпуск 5</t>
   </si>
   <si>
@@ -504,14 +506,14 @@
     <t>Выпуск 154</t>
   </si>
   <si>
-    <t>Выпуск 155</t>
+    <t>Выпуск 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,13 +906,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7C6AF9-5F0C-4EB9-8185-62F3B09665F4}">
   <dimension ref="A1:B155"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.375" customWidth="1"/>
-    <col min="2" max="2" width="39.625" customWidth="1"/>
+    <col min="1" max="1" width="49.42578125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -918,1387 +920,1233 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16.5">
-      <c r="A2" s="2" t="str">
-        <f>B2</f>
-        <v>Выпуск 1</v>
+    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16.5">
-      <c r="A3" s="2" t="str">
-        <f t="shared" ref="A3:A66" si="0">B3</f>
-        <v>Выпуск 2</v>
+    <row r="3" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.5">
-      <c r="A4" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 3</v>
+    <row r="4" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.5">
-      <c r="A5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 155</v>
+    <row r="5" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.5">
-      <c r="A6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 5</v>
+    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16.5">
-      <c r="A7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 6</v>
+    <row r="7" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.5">
-      <c r="A8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 7</v>
+    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="16.5">
-      <c r="A9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 8</v>
+    <row r="9" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.5">
-      <c r="A10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 9</v>
+    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16.5">
-      <c r="A11" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 10</v>
+    <row r="11" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.5">
-      <c r="A12" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 11</v>
+    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16.5">
-      <c r="A13" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 12</v>
+    <row r="13" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.5">
-      <c r="A14" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 13</v>
+    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="16.5">
-      <c r="A15" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 14</v>
+    <row r="15" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16.5">
-      <c r="A16" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 15</v>
+    <row r="16" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16.5">
-      <c r="A17" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 16</v>
+    <row r="17" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="16.5">
-      <c r="A18" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 17</v>
+    <row r="18" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16.5">
-      <c r="A19" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 18</v>
+    <row r="19" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16.5">
-      <c r="A20" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 19</v>
+    <row r="20" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16.5">
-      <c r="A21" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 20</v>
+    <row r="21" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="16.5">
-      <c r="A22" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 21</v>
+    <row r="22" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="16.5">
-      <c r="A23" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 22</v>
+    <row r="23" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="16.5">
-      <c r="A24" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 23</v>
+    <row r="24" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="16.5">
-      <c r="A25" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 24</v>
+    <row r="25" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="16.5">
-      <c r="A26" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 25</v>
+    <row r="26" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="16.5">
-      <c r="A27" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 26</v>
+    <row r="27" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16.5">
-      <c r="A28" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 27</v>
+    <row r="28" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16.5">
-      <c r="A29" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 28</v>
+    <row r="29" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="16.5">
-      <c r="A30" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 29</v>
+    <row r="30" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="16.5">
-      <c r="A31" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 30</v>
+    <row r="31" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="16.5">
-      <c r="A32" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 31</v>
+    <row r="32" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="16.5">
-      <c r="A33" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 32</v>
+    <row r="33" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="16.5">
-      <c r="A34" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 33</v>
+    <row r="34" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="16.5">
-      <c r="A35" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 34</v>
+    <row r="35" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="16.5">
-      <c r="A36" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 35</v>
+    <row r="36" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="16.5">
-      <c r="A37" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 36</v>
+    <row r="37" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16.5">
-      <c r="A38" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 37</v>
+    <row r="38" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16.5">
-      <c r="A39" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 38</v>
+    <row r="39" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16.5">
-      <c r="A40" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 39</v>
+    <row r="40" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16.5">
-      <c r="A41" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 40</v>
+    <row r="41" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16.5">
-      <c r="A42" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 41</v>
+    <row r="42" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16.5">
-      <c r="A43" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 42</v>
+    <row r="43" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="16.5">
-      <c r="A44" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 43</v>
+    <row r="44" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="16.5">
-      <c r="A45" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 44</v>
+    <row r="45" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="16.5">
-      <c r="A46" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 45</v>
+    <row r="46" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="16.5">
-      <c r="A47" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 46</v>
+    <row r="47" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="16.5">
-      <c r="A48" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 47</v>
+    <row r="48" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="16.5">
-      <c r="A49" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 48</v>
+    <row r="49" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="16.5">
-      <c r="A50" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 49</v>
+    <row r="50" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="16.5">
-      <c r="A51" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 50</v>
+    <row r="51" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="16.5">
-      <c r="A52" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 51</v>
+    <row r="52" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="16.5">
-      <c r="A53" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 52</v>
+    <row r="53" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="16.5">
-      <c r="A54" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 53</v>
+    <row r="54" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="16.5">
-      <c r="A55" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 54</v>
+    <row r="55" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="16.5">
-      <c r="A56" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 55</v>
+    <row r="56" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="16.5">
-      <c r="A57" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 56</v>
+    <row r="57" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="16.5">
-      <c r="A58" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 57</v>
+    <row r="58" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="16.5">
-      <c r="A59" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 58</v>
+    <row r="59" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="16.5">
-      <c r="A60" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 59</v>
+    <row r="60" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="16.5">
-      <c r="A61" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 60</v>
+    <row r="61" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="16.5">
-      <c r="A62" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 61</v>
+    <row r="62" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="16.5">
-      <c r="A63" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 62</v>
+    <row r="63" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="16.5">
-      <c r="A64" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 63</v>
+    <row r="64" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="16.5">
-      <c r="A65" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 64</v>
+    <row r="65" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="16.5">
-      <c r="A66" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Выпуск 65</v>
+    <row r="66" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="16.5">
-      <c r="A67" s="2" t="str">
-        <f t="shared" ref="A67:A130" si="1">B67</f>
-        <v>Выпуск 66</v>
+    <row r="67" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="16.5">
-      <c r="A68" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 67</v>
+    <row r="68" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="16.5">
-      <c r="A69" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 68</v>
+    <row r="69" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="16.5">
-      <c r="A70" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 69</v>
+    <row r="70" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="16.5">
-      <c r="A71" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 70</v>
+    <row r="71" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="16.5">
-      <c r="A72" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 71</v>
+    <row r="72" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="16.5">
-      <c r="A73" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 72</v>
+    <row r="73" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="16.5">
-      <c r="A74" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 73</v>
+    <row r="74" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="16.5">
-      <c r="A75" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 74</v>
+    <row r="75" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="16.5">
-      <c r="A76" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 75</v>
+    <row r="76" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="16.5">
-      <c r="A77" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 76</v>
+    <row r="77" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="16.5">
-      <c r="A78" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 77</v>
+    <row r="78" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="16.5">
-      <c r="A79" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 78</v>
+    <row r="79" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="16.5">
-      <c r="A80" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 79</v>
+    <row r="80" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="16.5">
-      <c r="A81" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 80</v>
+    <row r="81" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="16.5">
-      <c r="A82" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 81</v>
+    <row r="82" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="16.5">
-      <c r="A83" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 82</v>
+    <row r="83" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="16.5">
-      <c r="A84" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 83</v>
+    <row r="84" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="16.5">
-      <c r="A85" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 84</v>
+    <row r="85" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="16.5">
-      <c r="A86" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 85</v>
+    <row r="86" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="16.5">
-      <c r="A87" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 86</v>
+    <row r="87" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="16.5">
-      <c r="A88" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 87</v>
+    <row r="88" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="16.5">
-      <c r="A89" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 88</v>
+    <row r="89" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="16.5">
-      <c r="A90" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 89</v>
+    <row r="90" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="16.5">
-      <c r="A91" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 90</v>
+    <row r="91" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="16.5">
-      <c r="A92" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 91</v>
+    <row r="92" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="16.5">
-      <c r="A93" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 92</v>
+    <row r="93" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="16.5">
-      <c r="A94" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 93</v>
+    <row r="94" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="16.5">
-      <c r="A95" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 94</v>
+    <row r="95" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="16.5">
-      <c r="A96" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 95</v>
+    <row r="96" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="16.5">
-      <c r="A97" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 96</v>
+    <row r="97" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="16.5">
-      <c r="A98" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 97</v>
+    <row r="98" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="16.5">
-      <c r="A99" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 98</v>
+    <row r="99" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="16.5">
-      <c r="A100" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 99</v>
+    <row r="100" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="16.5">
-      <c r="A101" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 100</v>
+    <row r="101" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="16.5">
-      <c r="A102" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 101</v>
+    <row r="102" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="16.5">
-      <c r="A103" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 102</v>
+    <row r="103" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="16.5">
-      <c r="A104" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 103</v>
+    <row r="104" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="16.5">
-      <c r="A105" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 104</v>
+    <row r="105" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="16.5">
-      <c r="A106" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 105</v>
+    <row r="106" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="16.5">
-      <c r="A107" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 106</v>
+    <row r="107" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="16.5">
-      <c r="A108" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 107</v>
+    <row r="108" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="16.5">
-      <c r="A109" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 108</v>
+    <row r="109" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="16.5">
-      <c r="A110" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 109</v>
+    <row r="110" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="16.5">
-      <c r="A111" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 110</v>
+    <row r="111" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="16.5">
-      <c r="A112" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 111</v>
+    <row r="112" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="16.5">
-      <c r="A113" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 112</v>
+    <row r="113" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="16.5">
-      <c r="A114" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 113</v>
+    <row r="114" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="16.5">
-      <c r="A115" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 114</v>
+    <row r="115" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="16.5">
-      <c r="A116" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 115</v>
+    <row r="116" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="16.5">
-      <c r="A117" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 116</v>
+    <row r="117" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="16.5">
-      <c r="A118" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 117</v>
+    <row r="118" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="16.5">
-      <c r="A119" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 118</v>
+    <row r="119" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="16.5">
-      <c r="A120" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 119</v>
+    <row r="120" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="16.5">
-      <c r="A121" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 120</v>
+    <row r="121" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="16.5">
-      <c r="A122" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 121</v>
+    <row r="122" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="16.5">
-      <c r="A123" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 122</v>
+    <row r="123" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="16.5">
-      <c r="A124" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 123</v>
+    <row r="124" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="16.5">
-      <c r="A125" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 124</v>
+    <row r="125" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="16.5">
-      <c r="A126" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 125</v>
+    <row r="126" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="16.5">
-      <c r="A127" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 126</v>
+    <row r="127" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="16.5">
-      <c r="A128" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 127</v>
+    <row r="128" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="16.5">
-      <c r="A129" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 128</v>
+    <row r="129" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="16.5">
-      <c r="A130" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Выпуск 129</v>
+    <row r="130" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="16.5">
-      <c r="A131" s="2" t="str">
-        <f t="shared" ref="A131:A155" si="2">B131</f>
-        <v>Выпуск 130</v>
+    <row r="131" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="16.5">
-      <c r="A132" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 131</v>
+    <row r="132" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="16.5">
-      <c r="A133" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 132</v>
+    <row r="133" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="16.5">
-      <c r="A134" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 133</v>
+    <row r="134" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="16.5">
-      <c r="A135" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 134</v>
+    <row r="135" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="16.5">
-      <c r="A136" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 135</v>
+    <row r="136" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="16.5">
-      <c r="A137" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 136</v>
+    <row r="137" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="16.5">
-      <c r="A138" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 137</v>
+    <row r="138" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="16.5">
-      <c r="A139" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 138</v>
+    <row r="139" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="16.5">
-      <c r="A140" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 139</v>
+    <row r="140" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="16.5">
-      <c r="A141" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 140</v>
+    <row r="141" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="16.5">
-      <c r="A142" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 141</v>
+    <row r="142" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="16.5">
-      <c r="A143" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 142</v>
+    <row r="143" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="16.5">
-      <c r="A144" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 143</v>
+    <row r="144" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="16.5">
-      <c r="A145" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 144</v>
+    <row r="145" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="16.5">
-      <c r="A146" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 145</v>
+    <row r="146" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="16.5">
-      <c r="A147" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 146</v>
+    <row r="147" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="16.5">
-      <c r="A148" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 147</v>
+    <row r="148" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="16.5">
-      <c r="A149" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 148</v>
+    <row r="149" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="16.5">
-      <c r="A150" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 149</v>
+    <row r="150" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="16.5">
-      <c r="A151" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 150</v>
+    <row r="151" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="16.5">
-      <c r="A152" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 151</v>
+    <row r="152" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="16.5">
-      <c r="A153" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 152</v>
+    <row r="153" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="16.5">
-      <c r="A154" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 153</v>
+    <row r="154" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="16.5">
-      <c r="A155" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Выпуск 154</v>
+    <row r="155" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>154</v>
